--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/86.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/86.xlsx
@@ -426,13 +426,13 @@
         <v>-9.274656945412328</v>
       </c>
       <c r="E2">
-        <v>-7.985834663488055</v>
+        <v>-5.816894866670292</v>
       </c>
       <c r="F2">
-        <v>-6.178062813047154</v>
+        <v>-6.585520999503577</v>
       </c>
       <c r="G2">
-        <v>-11.51847494072967</v>
+        <v>-9.366070789643883</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.518137414627352</v>
       </c>
       <c r="E3">
-        <v>-9.092222376094062</v>
+        <v>-6.95644006596046</v>
       </c>
       <c r="F3">
-        <v>-6.347317325889357</v>
+        <v>-6.652406697075221</v>
       </c>
       <c r="G3">
-        <v>-10.48250923567108</v>
+        <v>-9.521802162356741</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.869905920714618</v>
       </c>
       <c r="E4">
-        <v>-9.388375519247687</v>
+        <v>-6.491293329788592</v>
       </c>
       <c r="F4">
-        <v>-6.655800104140789</v>
+        <v>-6.556493348974677</v>
       </c>
       <c r="G4">
-        <v>-10.67659658900193</v>
+        <v>-9.867101993739343</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.27145234473572</v>
       </c>
       <c r="E5">
-        <v>-11.3323497843124</v>
+        <v>-7.743651873557845</v>
       </c>
       <c r="F5">
-        <v>-6.11772204632503</v>
+        <v>-6.610498761800191</v>
       </c>
       <c r="G5">
-        <v>-10.84002829063913</v>
+        <v>-9.30599431974273</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.70152521511326</v>
       </c>
       <c r="E6">
-        <v>-11.03804425855391</v>
+        <v>-9.074583969834185</v>
       </c>
       <c r="F6">
-        <v>-6.187126809168586</v>
+        <v>-6.405989760662243</v>
       </c>
       <c r="G6">
-        <v>-10.83066275730854</v>
+        <v>-9.291487509189643</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.12403131412632</v>
       </c>
       <c r="E7">
-        <v>-12.91118413319064</v>
+        <v>-9.674923769031045</v>
       </c>
       <c r="F7">
-        <v>-5.888097773901603</v>
+        <v>-6.134285252544005</v>
       </c>
       <c r="G7">
-        <v>-9.827537663999513</v>
+        <v>-9.200910983235184</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.49985666704681</v>
       </c>
       <c r="E8">
-        <v>-12.45214177998111</v>
+        <v>-10.59036384662962</v>
       </c>
       <c r="F8">
-        <v>-5.618045030384548</v>
+        <v>-6.290628831046176</v>
       </c>
       <c r="G8">
-        <v>-10.32560592983732</v>
+        <v>-9.056793004274091</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.80350422962839</v>
       </c>
       <c r="E9">
-        <v>-13.44118767410037</v>
+        <v>-11.37892061100728</v>
       </c>
       <c r="F9">
-        <v>-6.169236558370325</v>
+        <v>-6.117739442040488</v>
       </c>
       <c r="G9">
-        <v>-10.98924782027624</v>
+        <v>-8.625369330687349</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.00328717128406</v>
       </c>
       <c r="E10">
-        <v>-15.31476681071585</v>
+        <v>-11.81578702700125</v>
       </c>
       <c r="F10">
-        <v>-5.805072994221217</v>
+        <v>-6.019968894222868</v>
       </c>
       <c r="G10">
-        <v>-9.745611593539168</v>
+        <v>-8.513181563452527</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.0806815928797</v>
       </c>
       <c r="E11">
-        <v>-15.59195470472535</v>
+        <v>-12.95468012603432</v>
       </c>
       <c r="F11">
-        <v>-5.724910223917504</v>
+        <v>-6.050126437889187</v>
       </c>
       <c r="G11">
-        <v>-9.300167759593613</v>
+        <v>-8.209793238597097</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.02821640114974</v>
       </c>
       <c r="E12">
-        <v>-15.16228856240358</v>
+        <v>-13.50566861549558</v>
       </c>
       <c r="F12">
-        <v>-5.521947784720583</v>
+        <v>-5.944951113857942</v>
       </c>
       <c r="G12">
-        <v>-9.49218602196242</v>
+        <v>-7.358367273534098</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.83821025260676</v>
       </c>
       <c r="E13">
-        <v>-15.70027580298882</v>
+        <v>-14.35067733685286</v>
       </c>
       <c r="F13">
-        <v>-5.600597956146784</v>
+        <v>-5.808064228912727</v>
       </c>
       <c r="G13">
-        <v>-10.07950990608452</v>
+        <v>-7.224545091200138</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.52904685416757</v>
       </c>
       <c r="E14">
-        <v>-16.88414117739206</v>
+        <v>-15.58341853122089</v>
       </c>
       <c r="F14">
-        <v>-4.876051496674947</v>
+        <v>-5.367926948415862</v>
       </c>
       <c r="G14">
-        <v>-9.099081912992741</v>
+        <v>-6.32533140127776</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.11441580802681</v>
       </c>
       <c r="E15">
-        <v>-18.50177549156802</v>
+        <v>-16.09728259076727</v>
       </c>
       <c r="F15">
-        <v>-5.134513723492032</v>
+        <v>-5.393913662209086</v>
       </c>
       <c r="G15">
-        <v>-8.378061647267174</v>
+        <v>-5.885508873657886</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.62396023898091</v>
       </c>
       <c r="E16">
-        <v>-19.04147449532817</v>
+        <v>-17.54446967176853</v>
       </c>
       <c r="F16">
-        <v>-4.512611925635886</v>
+        <v>-5.012086819930085</v>
       </c>
       <c r="G16">
-        <v>-7.253181310114834</v>
+        <v>-5.847195930131901</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.09145652902005</v>
       </c>
       <c r="E17">
-        <v>-19.36081342540107</v>
+        <v>-18.10446529603106</v>
       </c>
       <c r="F17">
-        <v>-4.858929142459081</v>
+        <v>-5.090232515607982</v>
       </c>
       <c r="G17">
-        <v>-7.568235997450655</v>
+        <v>-5.10951368870718</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.543935026327327</v>
       </c>
       <c r="E18">
-        <v>-20.82493699919101</v>
+        <v>-19.24825820394042</v>
       </c>
       <c r="F18">
-        <v>-4.291031929061046</v>
+        <v>-4.71224929807797</v>
       </c>
       <c r="G18">
-        <v>-7.144353746602373</v>
+        <v>-5.164015199920202</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.023167836960722</v>
       </c>
       <c r="E19">
-        <v>-21.1187670351787</v>
+        <v>-19.82039466701751</v>
       </c>
       <c r="F19">
-        <v>-4.222511034236277</v>
+        <v>-4.646472784458675</v>
       </c>
       <c r="G19">
-        <v>-7.07967892894717</v>
+        <v>-4.635784553674092</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.550666699925189</v>
       </c>
       <c r="E20">
-        <v>-22.80636174429916</v>
+        <v>-21.25275552411765</v>
       </c>
       <c r="F20">
-        <v>-3.641079125843901</v>
+        <v>-4.257964330708693</v>
       </c>
       <c r="G20">
-        <v>-6.238138252864434</v>
+        <v>-4.781266477397364</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.152219845740175</v>
       </c>
       <c r="E21">
-        <v>-23.34323498027852</v>
+        <v>-21.92345422397168</v>
       </c>
       <c r="F21">
-        <v>-3.048885068154354</v>
+        <v>-4.008045885284082</v>
       </c>
       <c r="G21">
-        <v>-6.587231969435043</v>
+        <v>-4.288548053151015</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.842549451266477</v>
       </c>
       <c r="E22">
-        <v>-23.56282068491045</v>
+        <v>-22.90151856862233</v>
       </c>
       <c r="F22">
-        <v>-3.053780719504899</v>
+        <v>-3.755922325833219</v>
       </c>
       <c r="G22">
-        <v>-7.342059526207648</v>
+        <v>-4.693335077328782</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.620716105019853</v>
       </c>
       <c r="E23">
-        <v>-24.07266798801203</v>
+        <v>-23.45264744077784</v>
       </c>
       <c r="F23">
-        <v>-3.219725076205516</v>
+        <v>-3.80674018089276</v>
       </c>
       <c r="G23">
-        <v>-6.233533284019309</v>
+        <v>-4.360234606258393</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.49011325461312</v>
       </c>
       <c r="E24">
-        <v>-25.49036111780133</v>
+        <v>-23.54408185946671</v>
       </c>
       <c r="F24">
-        <v>-3.18430739953142</v>
+        <v>-3.380817685027936</v>
       </c>
       <c r="G24">
-        <v>-6.574790939298461</v>
+        <v>-4.486078373842709</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.429159024173106</v>
       </c>
       <c r="E25">
-        <v>-24.58756906810618</v>
+        <v>-23.33696304377789</v>
       </c>
       <c r="F25">
-        <v>-2.845957420388351</v>
+        <v>-3.634469582336964</v>
       </c>
       <c r="G25">
-        <v>-6.682857077336891</v>
+        <v>-4.671104764032576</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.421122010545924</v>
       </c>
       <c r="E26">
-        <v>-25.27131430157631</v>
+        <v>-23.56517096292043</v>
       </c>
       <c r="F26">
-        <v>-2.287303958838156</v>
+        <v>-3.288060416732058</v>
       </c>
       <c r="G26">
-        <v>-6.672985030538784</v>
+        <v>-4.875775931452478</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.438638667402833</v>
       </c>
       <c r="E27">
-        <v>-26.16855444213806</v>
+        <v>-24.46855171423658</v>
       </c>
       <c r="F27">
-        <v>-2.680859655173395</v>
+        <v>-3.340357735972999</v>
       </c>
       <c r="G27">
-        <v>-7.82326718361395</v>
+        <v>-4.845871773596241</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.448067796432963</v>
       </c>
       <c r="E28">
-        <v>-24.8415077765603</v>
+        <v>-24.41744335658602</v>
       </c>
       <c r="F28">
-        <v>-2.722971368829514</v>
+        <v>-3.578607798161777</v>
       </c>
       <c r="G28">
-        <v>-7.816758651083743</v>
+        <v>-4.696225183584565</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.426340525364501</v>
       </c>
       <c r="E29">
-        <v>-25.41278835804994</v>
+        <v>-23.18925780706971</v>
       </c>
       <c r="F29">
-        <v>-2.72254724471928</v>
+        <v>-3.568062681124139</v>
       </c>
       <c r="G29">
-        <v>-7.660639944542793</v>
+        <v>-5.250019862484928</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.343417566566576</v>
       </c>
       <c r="E30">
-        <v>-25.01739370701821</v>
+        <v>-23.38606981591707</v>
       </c>
       <c r="F30">
-        <v>-2.920290969278565</v>
+        <v>-3.510414936828516</v>
       </c>
       <c r="G30">
-        <v>-6.944469628032257</v>
+        <v>-5.646576870452066</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.188481767358734</v>
       </c>
       <c r="E31">
-        <v>-24.19821992987469</v>
+        <v>-23.38057677694577</v>
       </c>
       <c r="F31">
-        <v>-2.789176148396056</v>
+        <v>-4.005706575738576</v>
       </c>
       <c r="G31">
-        <v>-7.347134592519351</v>
+        <v>-5.50393208425595</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.955685215884079</v>
       </c>
       <c r="E32">
-        <v>-23.80359511942428</v>
+        <v>-22.65870179233105</v>
       </c>
       <c r="F32">
-        <v>-2.893216609085465</v>
+        <v>-3.649390135996188</v>
       </c>
       <c r="G32">
-        <v>-6.813378645768196</v>
+        <v>-5.227309520085528</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.64887949935445</v>
       </c>
       <c r="E33">
-        <v>-23.36734910436936</v>
+        <v>-22.18983717899888</v>
       </c>
       <c r="F33">
-        <v>-3.04867963303846</v>
+        <v>-3.725594138481923</v>
       </c>
       <c r="G33">
-        <v>-7.119186979412833</v>
+        <v>-5.064381021370297</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.287281846182586</v>
       </c>
       <c r="E34">
-        <v>-21.82143223305287</v>
+        <v>-22.30952927549562</v>
       </c>
       <c r="F34">
-        <v>-3.036958234288847</v>
+        <v>-3.601732502578328</v>
       </c>
       <c r="G34">
-        <v>-7.020956472171578</v>
+        <v>-4.758632277545367</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.887287756408869</v>
       </c>
       <c r="E35">
-        <v>-22.73977959096438</v>
+        <v>-21.38384126121768</v>
       </c>
       <c r="F35">
-        <v>-3.015767767757833</v>
+        <v>-3.647758252212673</v>
       </c>
       <c r="G35">
-        <v>-7.533064761641438</v>
+        <v>-4.779445677350765</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.479765145441804</v>
       </c>
       <c r="E36">
-        <v>-22.65381556887677</v>
+        <v>-21.01524159088935</v>
       </c>
       <c r="F36">
-        <v>-2.818749693043401</v>
+        <v>-3.569764976136891</v>
       </c>
       <c r="G36">
-        <v>-6.573079387254658</v>
+        <v>-4.834096163113053</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.090191480446762</v>
       </c>
       <c r="E37">
-        <v>-23.07161258082444</v>
+        <v>-20.25188125589036</v>
       </c>
       <c r="F37">
-        <v>-3.096626366679898</v>
+        <v>-3.534142692714305</v>
       </c>
       <c r="G37">
-        <v>-6.484379940620965</v>
+        <v>-4.035946807413545</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.74393576991532</v>
       </c>
       <c r="E38">
-        <v>-21.06607824009945</v>
+        <v>-19.66870890165658</v>
       </c>
       <c r="F38">
-        <v>-2.846450298993016</v>
+        <v>-3.387489356090083</v>
       </c>
       <c r="G38">
-        <v>-6.359453194151028</v>
+        <v>-3.853754244205295</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.46690195764664</v>
       </c>
       <c r="E39">
-        <v>-20.38684789521497</v>
+        <v>-19.51889339606082</v>
       </c>
       <c r="F39">
-        <v>-2.832928029509717</v>
+        <v>-3.712211034722295</v>
       </c>
       <c r="G39">
-        <v>-6.278659330265114</v>
+        <v>-3.711347817288005</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.269821055407271</v>
       </c>
       <c r="E40">
-        <v>-21.48167441367939</v>
+        <v>-19.1774600413045</v>
       </c>
       <c r="F40">
-        <v>-3.267048877560049</v>
+        <v>-3.733789177197819</v>
       </c>
       <c r="G40">
-        <v>-5.907179704757955</v>
+        <v>-3.523530637208533</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.167438341348122</v>
       </c>
       <c r="E41">
-        <v>-20.53442633465094</v>
+        <v>-18.56725722571893</v>
       </c>
       <c r="F41">
-        <v>-3.010557336794224</v>
+        <v>-3.653150924004898</v>
       </c>
       <c r="G41">
-        <v>-5.40962788402427</v>
+        <v>-3.19481332843214</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.15718837873711</v>
       </c>
       <c r="E42">
-        <v>-18.54979090147135</v>
+        <v>-17.60915439449409</v>
       </c>
       <c r="F42">
-        <v>-2.847889173171679</v>
+        <v>-3.615152054503679</v>
       </c>
       <c r="G42">
-        <v>-5.874415235555788</v>
+        <v>-3.221761169121807</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.23383574844573</v>
       </c>
       <c r="E43">
-        <v>-18.71027549182918</v>
+        <v>-17.76814458842939</v>
       </c>
       <c r="F43">
-        <v>-3.349253573511663</v>
+        <v>-3.613939324625981</v>
       </c>
       <c r="G43">
-        <v>-6.406598673175789</v>
+        <v>-3.26244777379945</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.387290617969381</v>
       </c>
       <c r="E44">
-        <v>-18.57952486180571</v>
+        <v>-16.75884283007383</v>
       </c>
       <c r="F44">
-        <v>-2.64938335060182</v>
+        <v>-3.530752184934646</v>
       </c>
       <c r="G44">
-        <v>-5.537401699657981</v>
+        <v>-2.75152134908711</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.596528681879631</v>
       </c>
       <c r="E45">
-        <v>-17.62130429025667</v>
+        <v>-16.21712412690626</v>
       </c>
       <c r="F45">
-        <v>-3.540558398248987</v>
+        <v>-3.448231052635162</v>
       </c>
       <c r="G45">
-        <v>-5.947945762528541</v>
+        <v>-3.227415580902882</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.850691920647559</v>
       </c>
       <c r="E46">
-        <v>-17.85408143967295</v>
+        <v>-15.20692120222318</v>
       </c>
       <c r="F46">
-        <v>-3.284259038720611</v>
+        <v>-3.463365325084309</v>
       </c>
       <c r="G46">
-        <v>-6.527234952626831</v>
+        <v>-2.980326393488299</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.127185633249382</v>
       </c>
       <c r="E47">
-        <v>-15.99636554750634</v>
+        <v>-15.05720079458158</v>
       </c>
       <c r="F47">
-        <v>-3.595919848512883</v>
+        <v>-3.732137412596637</v>
       </c>
       <c r="G47">
-        <v>-6.088359241031188</v>
+        <v>-3.401649592634725</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.413149649807696</v>
       </c>
       <c r="E48">
-        <v>-15.40616953008666</v>
+        <v>-14.20609674720997</v>
       </c>
       <c r="F48">
-        <v>-3.194197277953443</v>
+        <v>-3.955053565792192</v>
       </c>
       <c r="G48">
-        <v>-6.006390133478834</v>
+        <v>-2.802917568584295</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.696197147826191</v>
       </c>
       <c r="E49">
-        <v>-15.2765419616171</v>
+        <v>-13.99154670567457</v>
       </c>
       <c r="F49">
-        <v>-3.536447210828893</v>
+        <v>-3.912491220268951</v>
       </c>
       <c r="G49">
-        <v>-5.04592141944332</v>
+        <v>-3.515591949005361</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.966279151018493</v>
       </c>
       <c r="E50">
-        <v>-14.82787434235915</v>
+        <v>-13.20190763600907</v>
       </c>
       <c r="F50">
-        <v>-3.528691206836481</v>
+        <v>-3.893279723463225</v>
       </c>
       <c r="G50">
-        <v>-5.183216364047975</v>
+        <v>-3.524292062682565</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.227590891350831</v>
       </c>
       <c r="E51">
-        <v>-14.5956496667718</v>
+        <v>-12.97164378966705</v>
       </c>
       <c r="F51">
-        <v>-3.749524016013996</v>
+        <v>-4.126419587144132</v>
       </c>
       <c r="G51">
-        <v>-5.820979720006412</v>
+        <v>-3.372520102434677</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.477062633338083</v>
       </c>
       <c r="E52">
-        <v>-13.64315308636846</v>
+        <v>-12.20973709482453</v>
       </c>
       <c r="F52">
-        <v>-3.825246737038704</v>
+        <v>-4.119973232015545</v>
       </c>
       <c r="G52">
-        <v>-6.451747893240369</v>
+        <v>-3.412796199465451</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.727564795354833</v>
       </c>
       <c r="E53">
-        <v>-13.60971030582181</v>
+        <v>-11.24840546163222</v>
       </c>
       <c r="F53">
-        <v>-3.628328066412608</v>
+        <v>-4.059692107746423</v>
       </c>
       <c r="G53">
-        <v>-6.481754678008323</v>
+        <v>-3.932796829500933</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.986999984767311</v>
       </c>
       <c r="E54">
-        <v>-13.15405525117002</v>
+        <v>-11.61339140970243</v>
       </c>
       <c r="F54">
-        <v>-3.604164589272947</v>
+        <v>-4.134688350558876</v>
       </c>
       <c r="G54">
-        <v>-5.558556085653924</v>
+        <v>-3.501114933362127</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.263679930665973</v>
       </c>
       <c r="E55">
-        <v>-12.49612684801762</v>
+        <v>-10.80689283130638</v>
       </c>
       <c r="F55">
-        <v>-3.997402192525511</v>
+        <v>-4.265413838762069</v>
       </c>
       <c r="G55">
-        <v>-6.557688661042587</v>
+        <v>-4.072227075978418</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.571846851155636</v>
       </c>
       <c r="E56">
-        <v>-12.30441390090289</v>
+        <v>-10.31902674103803</v>
       </c>
       <c r="F56">
-        <v>-3.661308686187668</v>
+        <v>-4.271323411813641</v>
       </c>
       <c r="G56">
-        <v>-6.449539759365675</v>
+        <v>-4.08098677947533</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.908462589360036</v>
       </c>
       <c r="E57">
-        <v>-11.6307309366778</v>
+        <v>-9.76930622429891</v>
       </c>
       <c r="F57">
-        <v>-4.042322900044523</v>
+        <v>-4.381189780446939</v>
       </c>
       <c r="G57">
-        <v>-5.473336022382005</v>
+        <v>-3.535293005509563</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.282513055580658</v>
       </c>
       <c r="E58">
-        <v>-11.70581756419899</v>
+        <v>-9.05591307150056</v>
       </c>
       <c r="F58">
-        <v>-4.002899238610489</v>
+        <v>-4.544563713096669</v>
       </c>
       <c r="G58">
-        <v>-6.596544534037013</v>
+        <v>-3.704471814202939</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.687688041460953</v>
       </c>
       <c r="E59">
-        <v>-10.59477005183909</v>
+        <v>-8.369256029243497</v>
       </c>
       <c r="F59">
-        <v>-4.182605262973813</v>
+        <v>-4.312665572152558</v>
       </c>
       <c r="G59">
-        <v>-6.460285790186149</v>
+        <v>-3.985182902114361</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.117615146857473</v>
       </c>
       <c r="E60">
-        <v>-10.19119697674951</v>
+        <v>-8.547397139757233</v>
       </c>
       <c r="F60">
-        <v>-4.245466751702657</v>
+        <v>-4.512807420342947</v>
       </c>
       <c r="G60">
-        <v>-5.977091805456284</v>
+        <v>-3.83633084303211</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.570918814078421</v>
       </c>
       <c r="E61">
-        <v>-10.83653622216059</v>
+        <v>-8.215269799086673</v>
       </c>
       <c r="F61">
-        <v>-4.514677873938468</v>
+        <v>-4.318233857834176</v>
       </c>
       <c r="G61">
-        <v>-6.563064986998363</v>
+        <v>-4.095496900573955</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.03034651499593</v>
       </c>
       <c r="E62">
-        <v>-9.975039326941381</v>
+        <v>-8.270793418894719</v>
       </c>
       <c r="F62">
-        <v>-4.188130473550486</v>
+        <v>-4.602353936585573</v>
       </c>
       <c r="G62">
-        <v>-6.429865187225786</v>
+        <v>-4.065102781977906</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.49622119862189</v>
       </c>
       <c r="E63">
-        <v>-9.52076545686193</v>
+        <v>-8.33591287512502</v>
       </c>
       <c r="F63">
-        <v>-4.379299446033751</v>
+        <v>-4.553366773486219</v>
       </c>
       <c r="G63">
-        <v>-7.071180758547862</v>
+        <v>-4.736478106796564</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.95407184962966</v>
       </c>
       <c r="E64">
-        <v>-10.35569379507814</v>
+        <v>-7.180341406321705</v>
       </c>
       <c r="F64">
-        <v>-4.417976748437862</v>
+        <v>-4.819584175928313</v>
       </c>
       <c r="G64">
-        <v>-7.557718394272391</v>
+        <v>-4.489428645928451</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.39452458594757</v>
       </c>
       <c r="E65">
-        <v>-8.124442195914829</v>
+        <v>-7.053132042972237</v>
       </c>
       <c r="F65">
-        <v>-4.507745267144439</v>
+        <v>-4.499273553716009</v>
       </c>
       <c r="G65">
-        <v>-7.157807803673971</v>
+        <v>-4.721587272960922</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.81255295737651</v>
       </c>
       <c r="E66">
-        <v>-9.3811797740495</v>
+        <v>-6.834977336126726</v>
       </c>
       <c r="F66">
-        <v>-4.526357854317941</v>
+        <v>-4.643870054079079</v>
       </c>
       <c r="G66">
-        <v>-7.40641653149108</v>
+        <v>-5.025495353466017</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.18883656445267</v>
       </c>
       <c r="E67">
-        <v>-9.164492292782473</v>
+        <v>-6.355126644851952</v>
       </c>
       <c r="F67">
-        <v>-4.470187917468913</v>
+        <v>-4.565692052072473</v>
       </c>
       <c r="G67">
-        <v>-7.059322384426192</v>
+        <v>-4.65309870684448</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.52042091323466</v>
       </c>
       <c r="E68">
-        <v>-9.571968912466659</v>
+        <v>-6.934685276827611</v>
       </c>
       <c r="F68">
-        <v>-4.321901868693772</v>
+        <v>-4.637473400994661</v>
       </c>
       <c r="G68">
-        <v>-6.749690370683697</v>
+        <v>-4.371255412358627</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.79070714527984</v>
       </c>
       <c r="E69">
-        <v>-8.760108620845525</v>
+        <v>-6.172683484030928</v>
       </c>
       <c r="F69">
-        <v>-4.783939526585851</v>
+        <v>-4.74254352236575</v>
       </c>
       <c r="G69">
-        <v>-7.687299767770543</v>
+        <v>-4.565528156239679</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.99294685111103</v>
       </c>
       <c r="E70">
-        <v>-9.013816377125258</v>
+        <v>-6.012986848150433</v>
       </c>
       <c r="F70">
-        <v>-4.348007039025596</v>
+        <v>-4.833702869941628</v>
       </c>
       <c r="G70">
-        <v>-7.851333988695892</v>
+        <v>-4.9478961660255</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-13.12701538799732</v>
       </c>
       <c r="E71">
-        <v>-9.291266922627203</v>
+        <v>-6.518328319614383</v>
       </c>
       <c r="F71">
-        <v>-4.931112249571627</v>
+        <v>-4.872057109058647</v>
       </c>
       <c r="G71">
-        <v>-7.364183902046597</v>
+        <v>-4.693762137703348</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.18442581095765</v>
       </c>
       <c r="E72">
-        <v>-10.27359256131907</v>
+        <v>-7.08057459545872</v>
       </c>
       <c r="F72">
-        <v>-4.739216798876107</v>
+        <v>-4.854217388671957</v>
       </c>
       <c r="G72">
-        <v>-6.45641907299628</v>
+        <v>-4.807730978438298</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-13.17702726009221</v>
       </c>
       <c r="E73">
-        <v>-9.460957900642628</v>
+        <v>-6.868161993654934</v>
       </c>
       <c r="F73">
-        <v>-4.732409275559902</v>
+        <v>-4.807474272866787</v>
       </c>
       <c r="G73">
-        <v>-7.239584899585047</v>
+        <v>-4.568567237044729</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-13.10338347459816</v>
       </c>
       <c r="E74">
-        <v>-9.814604549797636</v>
+        <v>-6.788483493489974</v>
       </c>
       <c r="F74">
-        <v>-4.887529355408136</v>
+        <v>-4.774095208370981</v>
       </c>
       <c r="G74">
-        <v>-6.175059118159162</v>
+        <v>-4.488673841545498</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.96889031648773</v>
       </c>
       <c r="E75">
-        <v>-9.301759396902977</v>
+        <v>-6.982515019296626</v>
       </c>
       <c r="F75">
-        <v>-4.860536175220513</v>
+        <v>-5.185229689361028</v>
       </c>
       <c r="G75">
-        <v>-6.891927959778484</v>
+        <v>-3.911380910407388</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.78152086901508</v>
       </c>
       <c r="E76">
-        <v>-10.57310130371238</v>
+        <v>-8.286516280649352</v>
       </c>
       <c r="F76">
-        <v>-4.994342361794716</v>
+        <v>-5.250867865624055</v>
       </c>
       <c r="G76">
-        <v>-6.295602702335104</v>
+        <v>-3.672117852647641</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.53931296295806</v>
       </c>
       <c r="E77">
-        <v>-10.19663567403272</v>
+        <v>-7.831214446970158</v>
       </c>
       <c r="F77">
-        <v>-5.097500611200144</v>
+        <v>-5.124722420790942</v>
       </c>
       <c r="G77">
-        <v>-6.507530585577088</v>
+        <v>-3.447348363258824</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.26295363417173</v>
       </c>
       <c r="E78">
-        <v>-11.05630759422684</v>
+        <v>-8.758763664065247</v>
       </c>
       <c r="F78">
-        <v>-5.096996963819242</v>
+        <v>-5.250814021742874</v>
       </c>
       <c r="G78">
-        <v>-6.52146798229742</v>
+        <v>-3.289259882122007</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.9579349539504</v>
       </c>
       <c r="E79">
-        <v>-11.41880288159284</v>
+        <v>-9.125230423135971</v>
       </c>
       <c r="F79">
-        <v>-5.12049360519965</v>
+        <v>-5.365392972530699</v>
       </c>
       <c r="G79">
-        <v>-6.039816711788855</v>
+        <v>-3.122580535310782</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.63931617029196</v>
       </c>
       <c r="E80">
-        <v>-13.50589956766997</v>
+        <v>-9.320484636924693</v>
       </c>
       <c r="F80">
-        <v>-5.318243956698156</v>
+        <v>-5.573494603094588</v>
       </c>
       <c r="G80">
-        <v>-4.807866710805407</v>
+        <v>-2.801361612180838</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.32307810292938</v>
       </c>
       <c r="E81">
-        <v>-12.50232180046011</v>
+        <v>-10.31116078168671</v>
       </c>
       <c r="F81">
-        <v>-5.187067008260438</v>
+        <v>-5.351828456309857</v>
       </c>
       <c r="G81">
-        <v>-5.388569503848966</v>
+        <v>-2.72612615425536</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.01017406563322</v>
       </c>
       <c r="E82">
-        <v>-13.60083902524078</v>
+        <v>-11.07966999163241</v>
       </c>
       <c r="F82">
-        <v>-5.2166455231122</v>
+        <v>-5.522552492924627</v>
       </c>
       <c r="G82">
-        <v>-5.713026140516318</v>
+        <v>-2.881208660042519</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.72101297639475</v>
       </c>
       <c r="E83">
-        <v>-14.74141218813069</v>
+        <v>-12.18514748096288</v>
       </c>
       <c r="F83">
-        <v>-5.620892957515372</v>
+        <v>-6.090704843482723</v>
       </c>
       <c r="G83">
-        <v>-5.329893394710924</v>
+        <v>-2.301565241571527</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.45730014829054</v>
       </c>
       <c r="E84">
-        <v>-14.75113029335115</v>
+        <v>-12.22121224795996</v>
       </c>
       <c r="F84">
-        <v>-5.302462729307424</v>
+        <v>-5.914966698978809</v>
       </c>
       <c r="G84">
-        <v>-5.390737911177189</v>
+        <v>-2.804480146078831</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.23201726922489</v>
       </c>
       <c r="E85">
-        <v>-15.55439554130573</v>
+        <v>-13.34837207083915</v>
       </c>
       <c r="F85">
-        <v>-5.654951283281474</v>
+        <v>-6.401637104144234</v>
       </c>
       <c r="G85">
-        <v>-4.836171875166176</v>
+        <v>-2.698698284462499</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.05156467513227</v>
       </c>
       <c r="E86">
-        <v>-17.49237410678429</v>
+        <v>-14.39330839116107</v>
       </c>
       <c r="F86">
-        <v>-5.876205731467014</v>
+        <v>-5.839366576329715</v>
       </c>
       <c r="G86">
-        <v>-4.807691251891827</v>
+        <v>-2.060408551763317</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.911237964106032</v>
       </c>
       <c r="E87">
-        <v>-19.14297571173609</v>
+        <v>-16.35876120844417</v>
       </c>
       <c r="F87">
-        <v>-5.905354323636723</v>
+        <v>-6.063082932436374</v>
       </c>
       <c r="G87">
-        <v>-4.576995885987714</v>
+        <v>-1.709957511521609</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.821855604039394</v>
       </c>
       <c r="E88">
-        <v>-19.76185961199436</v>
+        <v>-17.65466555827118</v>
       </c>
       <c r="F88">
-        <v>-5.822801713375933</v>
+        <v>-6.083744900564402</v>
       </c>
       <c r="G88">
-        <v>-5.091676469341587</v>
+        <v>-1.712701953773665</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.771136712845157</v>
       </c>
       <c r="E89">
-        <v>-20.65621058613922</v>
+        <v>-18.24242978514874</v>
       </c>
       <c r="F89">
-        <v>-6.223308240588063</v>
+        <v>-6.158202704565036</v>
       </c>
       <c r="G89">
-        <v>-4.758890500097429</v>
+        <v>-1.883757841787807</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.76086435595265</v>
       </c>
       <c r="E90">
-        <v>-22.96762976066031</v>
+        <v>-20.182591075099</v>
       </c>
       <c r="F90">
-        <v>-6.066511545116561</v>
+        <v>-6.40482880374722</v>
       </c>
       <c r="G90">
-        <v>-5.62562111718848</v>
+        <v>-2.17591017508295</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.784719052866748</v>
       </c>
       <c r="E91">
-        <v>-23.02761392736591</v>
+        <v>-22.35296186970318</v>
       </c>
       <c r="F91">
-        <v>-5.977080171942924</v>
+        <v>-6.217905628387005</v>
       </c>
       <c r="G91">
-        <v>-4.418698840481922</v>
+        <v>-2.88783637221214</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.831990132002895</v>
       </c>
       <c r="E92">
-        <v>-26.29004887128985</v>
+        <v>-24.17013886255313</v>
       </c>
       <c r="F92">
-        <v>-6.12250089787178</v>
+        <v>-6.696809674967483</v>
       </c>
       <c r="G92">
-        <v>-5.769216029954368</v>
+        <v>-2.125301865424111</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.905059576245563</v>
       </c>
       <c r="E93">
-        <v>-28.50526514399199</v>
+        <v>-25.59577493575188</v>
       </c>
       <c r="F93">
-        <v>-6.211064970374686</v>
+        <v>-6.530863247348359</v>
       </c>
       <c r="G93">
-        <v>-5.232917584229053</v>
+        <v>-2.362545490404902</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.986770316175832</v>
       </c>
       <c r="E94">
-        <v>-30.10791247343957</v>
+        <v>-27.97749866924206</v>
       </c>
       <c r="F94">
-        <v>-6.533385626089884</v>
+        <v>-6.259850011827758</v>
       </c>
       <c r="G94">
-        <v>-5.166243197068131</v>
+        <v>-2.544804264523938</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.07545498128532</v>
       </c>
       <c r="E95">
-        <v>-32.89277681275159</v>
+        <v>-30.62519779509875</v>
       </c>
       <c r="F95">
-        <v>-6.165957880190045</v>
+        <v>-6.265192981575814</v>
       </c>
       <c r="G95">
-        <v>-6.882966313003677</v>
+        <v>-3.256293469641945</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.15531544808613</v>
       </c>
       <c r="E96">
-        <v>-35.54278093187818</v>
+        <v>-33.05068922987306</v>
       </c>
       <c r="F96">
-        <v>-6.159444427301832</v>
+        <v>-6.348270776769979</v>
       </c>
       <c r="G96">
-        <v>-6.398785785703109</v>
+        <v>-3.860948059662131</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.21436143153908</v>
       </c>
       <c r="E97">
-        <v>-35.97900883303707</v>
+        <v>-35.8930697175565</v>
       </c>
       <c r="F97">
-        <v>-6.169958066378164</v>
+        <v>-6.28559981254378</v>
       </c>
       <c r="G97">
-        <v>-6.550335939399865</v>
+        <v>-4.229696485099391</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.24758435920222</v>
       </c>
       <c r="E98">
-        <v>-39.13088787677474</v>
+        <v>-38.00231064153115</v>
       </c>
       <c r="F98">
-        <v>-6.565139847925098</v>
+        <v>-6.26106108497065</v>
       </c>
       <c r="G98">
-        <v>-7.112483124695808</v>
+        <v>-4.641700498552769</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.24637834928156</v>
       </c>
       <c r="E99">
-        <v>-41.98404160412243</v>
+        <v>-40.72081019426076</v>
       </c>
       <c r="F99">
-        <v>-6.759691872881396</v>
+        <v>-6.250542475689902</v>
       </c>
       <c r="G99">
-        <v>-6.846374853158112</v>
+        <v>-5.329055826689489</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.21017984597365</v>
       </c>
       <c r="E100">
-        <v>-43.26288945659955</v>
+        <v>-43.68745427295168</v>
       </c>
       <c r="F100">
-        <v>-6.706277500197779</v>
+        <v>-6.402424467360595</v>
       </c>
       <c r="G100">
-        <v>-7.552795613055495</v>
+        <v>-5.650854095288805</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.14787769793181</v>
       </c>
       <c r="E101">
-        <v>-46.91744949332167</v>
+        <v>-45.77873979748591</v>
       </c>
       <c r="F101">
-        <v>-6.591947887998197</v>
+        <v>-6.424181123011422</v>
       </c>
       <c r="G101">
-        <v>-8.04025689098548</v>
+        <v>-5.544883532576734</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.041632241863</v>
       </c>
       <c r="E102">
-        <v>-49.49848382119294</v>
+        <v>-47.80461151497935</v>
       </c>
       <c r="F102">
-        <v>-6.634080725023087</v>
+        <v>-6.14215142940099</v>
       </c>
       <c r="G102">
-        <v>-8.737351844098736</v>
+        <v>-6.487733523252246</v>
       </c>
     </row>
   </sheetData>
